--- a/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.112.xlsx
+++ b/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.112.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="oocihm.22250.112" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="oocihm.22250.112" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -581,19 +581,15 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.112.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.112.txt</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0112.txt</t>
-        </is>
-      </c>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t>L76: possible duplicated/overlap line with previous line (similarity 64%) :: or such proceedings as might have been taken if no such</t>
-        </is>
-      </c>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0112.txt</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr"/>
       <c r="E2" s="1" t="inlineStr"/>
       <c r="F2" s="1" t="inlineStr">
         <is>
@@ -734,7 +730,7 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
@@ -815,12 +811,12 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C7" s="1" t="inlineStr">

--- a/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.112.xlsx
+++ b/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.112.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="oocihm.22250.112" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="oocihm.22250.112" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -422,8 +422,8 @@
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="27" customWidth="1" min="8" max="8"/>
@@ -431,9 +431,9 @@
     <col width="27" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="51" customWidth="1" min="14" max="14"/>
-    <col width="50" customWidth="1" min="15" max="15"/>
+    <col width="60" customWidth="1" min="15" max="15"/>
     <col width="31" customWidth="1" min="16" max="16"/>
     <col width="30" customWidth="1" min="17" max="17"/>
     <col width="30" customWidth="1" min="18" max="18"/>
@@ -602,11 +602,15 @@
       <c r="J2" s="1" t="inlineStr"/>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L96: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE :: ly enoughâ€˜</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]3</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]3</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L55: symbol-only separator/garbage line :: 1850.</t>
@@ -614,7 +618,7 @@
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>L27: isolated marker/symbol line :: I</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]3</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr"/>
@@ -641,7 +645,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>80</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -661,7 +665,7 @@
       </c>
       <c r="O3" s="1" t="inlineStr">
         <is>
-          <t>L29: isolated marker/symbol line :: %</t>
+          <t>L27: isolated marker/symbol line :: I</t>
         </is>
       </c>
       <c r="P3" s="1" t="inlineStr"/>
@@ -708,7 +712,7 @@
       </c>
       <c r="O4" s="1" t="inlineStr">
         <is>
-          <t>L35: isolated marker/symbol line :: -</t>
+          <t>L29: isolated marker/symbol line :: %</t>
         </is>
       </c>
       <c r="P4" s="1" t="inlineStr"/>
@@ -751,7 +755,7 @@
       <c r="N5" s="1" t="inlineStr"/>
       <c r="O5" s="1" t="inlineStr">
         <is>
-          <t>L42: isolated marker/symbol line :: /</t>
+          <t>L35: isolated marker/symbol line :: -</t>
         </is>
       </c>
       <c r="P5" s="1" t="inlineStr"/>
@@ -794,7 +798,7 @@
       <c r="N6" s="1" t="inlineStr"/>
       <c r="O6" s="1" t="inlineStr">
         <is>
-          <t>L80: symbol-only separator/garbage line :: 1850.</t>
+          <t>L42: isolated marker/symbol line :: /</t>
         </is>
       </c>
       <c r="P6" s="1" t="inlineStr"/>
@@ -837,7 +841,7 @@
       <c r="N7" s="1" t="inlineStr"/>
       <c r="O7" s="1" t="inlineStr">
         <is>
-          <t>L83: isolated marker/symbol line :: +</t>
+          <t>L80: symbol-only separator/garbage line :: 1850.</t>
         </is>
       </c>
       <c r="P7" s="1" t="inlineStr"/>
@@ -880,7 +884,7 @@
       <c r="N8" s="1" t="inlineStr"/>
       <c r="O8" s="1" t="inlineStr">
         <is>
-          <t>L85: isolated marker/symbol line :: /</t>
+          <t>L83: isolated marker/symbol line :: +</t>
         </is>
       </c>
       <c r="P8" s="1" t="inlineStr"/>
@@ -923,7 +927,7 @@
       <c r="N9" s="1" t="inlineStr"/>
       <c r="O9" s="1" t="inlineStr">
         <is>
-          <t>L102: isolated marker/symbol line :: 9</t>
+          <t>L85: isolated marker/symbol line :: /</t>
         </is>
       </c>
       <c r="P9" s="1" t="inlineStr"/>
@@ -964,7 +968,11 @@
       <c r="L10" s="1" t="inlineStr"/>
       <c r="M10" s="1" t="inlineStr"/>
       <c r="N10" s="1" t="inlineStr"/>
-      <c r="O10" s="1" t="inlineStr"/>
+      <c r="O10" s="1" t="inlineStr">
+        <is>
+          <t>L102: isolated marker/symbol line :: 9</t>
+        </is>
+      </c>
       <c r="P10" s="1" t="inlineStr"/>
       <c r="Q10" s="1" t="inlineStr"/>
       <c r="R10" s="1" t="inlineStr"/>
@@ -989,7 +997,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1028,7 +1036,7 @@
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
